--- a/output/Data and Chart Outputs/chile_gas_imports.xlsx
+++ b/output/Data and Chart Outputs/chile_gas_imports.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gas imports" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gas imports" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,13 +141,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -171,22 +171,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$12</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$12</f>
+              <f>'Chart'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -208,8 +208,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -222,8 +222,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -239,7 +239,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -252,7 +252,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -261,7 +261,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -276,9 +276,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -603,29 +603,52 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MoM_change_published / YoY_change_published: the report's own change on the previous month and on the same month a year earlier (fractions; blank where the report shows n/d or n/a).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>COVERAGE</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Monthly from 2021. The data month lags the report by about two months; it is read from the report's own text. Origins lists the source countries the report names for that month's gas imports.</t>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Monthly from January 2021. The data month lags the report by about two months; it is read from the report's own text where the text can be read ('month stated'), otherwise taken as report month - 2. Each month is checked against the following month's published monthly change (see the run log).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>SOURCE</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Method: 'text' = PDF text layer; 'text+ocr' = table from the text layer, data month and origins by OCR; 'ocr' = the whole page by OCR (reports from 2021-2025 that have no text layer); p&lt;n&gt; = PDF page. 'derived' = month with no CNE report (e.g. no May 2026 report was published), computed from the next month's value and its published monthly change.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>Origins lists the source countries the report names for that month's gas imports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Comision Nacional de Energia (CNE), Reporte Mensual del Sector Energetico, section 'Importaciones y Exportaciones de Combustibles' (Aduana data via COMEX). The Report column holds the PDF used.</t>
         </is>
@@ -642,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -662,89 +685,361 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45870</v>
+        <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>16.63</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45901</v>
+        <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>19.54</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45931</v>
+        <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>13.29</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45962</v>
+        <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>18.18</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45992</v>
+        <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>18.12</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46023</v>
+        <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>18.82</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46054</v>
+        <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>21.61</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46113</v>
+        <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>19.77</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46143</v>
+        <v>44470</v>
       </c>
       <c r="B10" t="n">
-        <v>20.22</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46174</v>
+        <v>44501</v>
       </c>
       <c r="B11" t="n">
-        <v>20.17</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B12" t="n">
+        <v>18.73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B13" t="n">
+        <v>15.97</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B14" t="n">
+        <v>21.48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B15" t="n">
+        <v>19.22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B17" t="n">
+        <v>24.39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B19" t="n">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B20" t="n">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B21" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B22" t="n">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B23" t="n">
+        <v>17.94</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B24" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B25" t="n">
+        <v>19.61</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B27" t="n">
+        <v>20.84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B28" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B29" t="n">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B30" t="n">
+        <v>18.95</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B34" t="n">
+        <v>21.76</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B35" t="n">
+        <v>16.63</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B36" t="n">
+        <v>19.54</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B37" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B38" t="n">
+        <v>18.18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B39" t="n">
+        <v>18.12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B40" t="n">
+        <v>18.82</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B41" t="n">
+        <v>21.61</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B42" t="n">
+        <v>20.46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B43" t="n">
+        <v>19.77</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B44" t="n">
+        <v>20.22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B45" t="n">
+        <v>20.17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B46" t="n">
         <v>22.55</v>
       </c>
     </row>
@@ -760,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,10 +1076,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>MoM_change_published</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>YoY_change_published</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Origins</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Report</t>
         </is>
@@ -796,23 +1106,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>379</v>
+        <v>215</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Nigeria, Estados Unidos, Trinidad y Tobago y Argentina</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/10/RMensual_v202510.pdf</t>
+        <v>9.43</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.256</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.481</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/03/RMensual_v202103.pdf</t>
         </is>
       </c>
     </row>
@@ -822,23 +1138,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="D3" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Estados Unidos, Nigeria, Trinidad y Tobago y Argentina</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/11/RMensual_v202511.pdf</t>
+        <v>19.77</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.078</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/04/RMensual_v202104.pdf</t>
         </is>
       </c>
     </row>
@@ -848,23 +1170,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>303</v>
+        <v>384</v>
       </c>
       <c r="D4" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/12/RMensual_v202512.pdf</t>
+        <v>16.85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/05/RMensual_v202105.pdf</t>
         </is>
       </c>
     </row>
@@ -874,23 +1202,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>401</v>
+        <v>358</v>
       </c>
       <c r="D5" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/01/RMensual_v202601.pdf</t>
+        <v>16.23</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/06/RMensual_v202106.pdf</t>
         </is>
       </c>
     </row>
@@ -900,23 +1234,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="D6" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/02/RMensual_v202602.pdf</t>
+        <v>15.35</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/07/RMensual_v202107.pdf</t>
         </is>
       </c>
     </row>
@@ -926,23 +1266,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>429</v>
+        <v>372</v>
       </c>
       <c r="D7" t="n">
-        <v>18.82</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Trinidad y Tobago, Estados Unidos, y Argentina</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/03/RMensual_v202603.pdf</t>
+        <v>16.86</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/08/RMensual_v202108.pdf</t>
         </is>
       </c>
     </row>
@@ -952,23 +1298,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>445</v>
+        <v>265</v>
       </c>
       <c r="D8" t="n">
-        <v>21.61</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Australia y Argentina</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/04/RMensual_v202604.pdf</t>
+        <v>11.63</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.289</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/09/RMensual_v202109.pdf</t>
         </is>
       </c>
     </row>
@@ -978,23 +1330,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D9" t="n">
-        <v>19.77</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/RMensual_v202606.pdf</t>
+        <v>18.73</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2021/12/RMensual_v202112.pdf</t>
         </is>
       </c>
     </row>
@@ -1004,18 +1362,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>461</v>
+        <v>275.8</v>
       </c>
       <c r="D10" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/07/RMensual_v202607.pdf</t>
+        <v>12.1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>derived: 2021-11 value / (1 + its monthly change +54.8%)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/01/RMensual_v202201.pdf</t>
         </is>
       </c>
     </row>
@@ -1025,18 +1388,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="D11" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/08/RMensual_v202608.pdf</t>
+        <v>19.36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month assumed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/01/RMensual_v202201.pdf</t>
         </is>
       </c>
     </row>
@@ -1046,21 +1420,1149 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>427</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month assumed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/02/RMensual_v202202.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>364</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/03/RMensual_v202203.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>489.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>derived: 2022-06 value / (1 + its monthly change -13.4%)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/08/RMensual_v202208.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>424</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.134</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/08/RMensual_v202208.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>336</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.208</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/09/RMensual_v202209.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>556</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>text+ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/10/RMensual_v202210.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>61</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ocr p16; month stated</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2022/11/RMensual_v202211.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>400.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>derived: 2023-07 value / (1 + its monthly change -8.6%)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2023/09/RMensual_v202309.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>366</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Guinea Ecuatorial, Estados Unidos , Argentina y Trinidad y Tobago</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2023/09/RMensual_v202309.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>344.1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>derived: 2024-01 value / (1 + its monthly change +1.7%)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/03/RMensual_v202403.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>350</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Guinea Ecuatorial, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/03/RMensual_v202403.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>409</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>derived: 2024-04 value / (1 + its monthly change -11.0%)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/06/RMensual_v202406.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>364</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/06/RMensual_v202406.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>447</v>
+      </c>
+      <c r="D25" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Argentina y Trinidad y Tobago</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/07/RMensual_v202407.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>374</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.163</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.064</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/08/RMensual_v202408.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>475</v>
+      </c>
+      <c r="D27" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>derived: 2024-08 value / (1 + its monthly change -38.1%)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/10/RMensual_v202410.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>294</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.381</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/10/RMensual_v202410.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>317</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/11/RMensual_v202411.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>432</v>
+      </c>
+      <c r="D30" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Argentina y Trinidad y Tobago</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>text+ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2024/12/RMensual_v202412.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/04/RMensual_v202504.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nigeria, Estados Unidos, Trinidad y Tobago, y Argentina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/06/RMensual_v202506.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nigeria, Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/08/RMensual_v202508.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>496.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>derived: 2025-08 value / (1 + its monthly change -23.6%)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/10/RMensual_v202510.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>379</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.236</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nigeria, Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/10/RMensual_v202510.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>431</v>
+      </c>
+      <c r="D36" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Nigeria, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/11/RMensual_v202511.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>303</v>
+      </c>
+      <c r="D37" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.298</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/12/RMensual_v202512.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>401</v>
+      </c>
+      <c r="D38" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/01/RMensual_v202601.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>413</v>
+      </c>
+      <c r="D39" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/02/RMensual_v202602.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>429</v>
+      </c>
+      <c r="D40" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos, y Argentina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/03/RMensual_v202603.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>445</v>
+      </c>
+      <c r="D41" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Australia y Argentina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/04/RMensual_v202604.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>466.3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>derived: 2026-04 value / (1 + its monthly change -6.5%)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/06/RMensual_v202606.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>436</v>
+      </c>
+      <c r="D43" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.142</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>text p17; month stated</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/06/RMensual_v202606.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>461</v>
+      </c>
+      <c r="D44" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>text p17; month stated</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/07/RMensual_v202607.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>445</v>
+      </c>
+      <c r="D45" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>text p17; month stated</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/08/RMensual_v202608.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C46" t="n">
         <v>514</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D46" t="n">
         <v>22.55</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E46" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>text p17; month stated</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>https://www.cne.cl/wp-content/uploads/2026/09/RMensual_v202609.pdf</t>
         </is>

--- a/output/Data and Chart Outputs/chile_gas_imports.xlsx
+++ b/output/Data and Chart Outputs/chile_gas_imports.xlsx
@@ -181,12 +181,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$46</f>
+              <f>'Chart'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$46</f>
+              <f>'Chart'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -208,8 +208,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="5"/>
+        <tickMarkSkip val="5"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -628,7 +628,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Method: 'text' = PDF text layer; 'text+ocr' = table from the text layer, data month and origins by OCR; 'ocr' = the whole page by OCR (reports from 2021-2025 that have no text layer); p&lt;n&gt; = PDF page. 'derived' = month with no CNE report (e.g. no May 2026 report was published), computed from the next month's value and its published monthly change.</t>
+          <t>Method: 'text' = PDF text layer; 'text+ocr' = table from the text layer, data month and origins by OCR; 'ocr' = the whole page by OCR (reports from 2021-2025 that have no text layer); p&lt;n&gt; = PDF page. 'derived' = month with no table of its own, computed from the next month's value and its published monthly change, or else from the same month a year later and its published annual change. This covers months where CNE published no report (no May 2026 report) or a report that repeated an earlier report's table (e.g. the Nov 2021-Feb 2022 reports all repeat Aug 2021's table). OCR'd changes are only kept when they read cleanly, so a few months may still have no value (see the run log).</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -749,297 +749,449 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>44470</v>
+        <v>44531</v>
       </c>
       <c r="B10" t="n">
-        <v>12.1</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>44501</v>
+        <v>44562</v>
       </c>
       <c r="B11" t="n">
-        <v>19.36</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>44531</v>
+        <v>44593</v>
       </c>
       <c r="B12" t="n">
-        <v>18.73</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>44562</v>
+        <v>44621</v>
       </c>
       <c r="B13" t="n">
-        <v>15.97</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>44682</v>
+        <v>44652</v>
       </c>
       <c r="B14" t="n">
-        <v>21.48</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>44713</v>
+        <v>44682</v>
       </c>
       <c r="B15" t="n">
-        <v>19.22</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>44743</v>
+        <v>44713</v>
       </c>
       <c r="B16" t="n">
-        <v>14.74</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>44774</v>
+        <v>44743</v>
       </c>
       <c r="B17" t="n">
-        <v>24.39</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>44805</v>
+        <v>44774</v>
       </c>
       <c r="B18" t="n">
-        <v>2.77</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45078</v>
+        <v>44805</v>
       </c>
       <c r="B19" t="n">
-        <v>18.15</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45108</v>
+        <v>44835</v>
       </c>
       <c r="B20" t="n">
-        <v>16.06</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45261</v>
+        <v>44866</v>
       </c>
       <c r="B21" t="n">
-        <v>15.1</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45292</v>
+        <v>44896</v>
       </c>
       <c r="B22" t="n">
-        <v>15.35</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45352</v>
+        <v>44927</v>
       </c>
       <c r="B23" t="n">
-        <v>17.94</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45383</v>
+        <v>44958</v>
       </c>
       <c r="B24" t="n">
-        <v>16.5</v>
+        <v>21.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45413</v>
+        <v>44986</v>
       </c>
       <c r="B25" t="n">
-        <v>19.61</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45444</v>
+        <v>45017</v>
       </c>
       <c r="B26" t="n">
-        <v>16.95</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45474</v>
+        <v>45047</v>
       </c>
       <c r="B27" t="n">
-        <v>20.84</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45505</v>
+        <v>45078</v>
       </c>
       <c r="B28" t="n">
-        <v>12.9</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45536</v>
+        <v>45108</v>
       </c>
       <c r="B29" t="n">
-        <v>14.37</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45566</v>
+        <v>45139</v>
       </c>
       <c r="B30" t="n">
-        <v>18.95</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45689</v>
+        <v>45170</v>
       </c>
       <c r="B31" t="n">
-        <v>0.47</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45748</v>
+        <v>45200</v>
       </c>
       <c r="B32" t="n">
-        <v>0.57</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45809</v>
+        <v>45231</v>
       </c>
       <c r="B33" t="n">
-        <v>1.81</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45839</v>
+        <v>45261</v>
       </c>
       <c r="B34" t="n">
-        <v>21.76</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45870</v>
+        <v>45292</v>
       </c>
       <c r="B35" t="n">
-        <v>16.63</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45901</v>
+        <v>45323</v>
       </c>
       <c r="B36" t="n">
-        <v>19.54</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45931</v>
+        <v>45352</v>
       </c>
       <c r="B37" t="n">
-        <v>13.29</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45962</v>
+        <v>45383</v>
       </c>
       <c r="B38" t="n">
-        <v>18.18</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45992</v>
+        <v>45413</v>
       </c>
       <c r="B39" t="n">
-        <v>18.12</v>
+        <v>19.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46023</v>
+        <v>45444</v>
       </c>
       <c r="B40" t="n">
-        <v>18.82</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46054</v>
+        <v>45474</v>
       </c>
       <c r="B41" t="n">
-        <v>21.61</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46082</v>
+        <v>45505</v>
       </c>
       <c r="B42" t="n">
-        <v>20.46</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46113</v>
+        <v>45536</v>
       </c>
       <c r="B43" t="n">
-        <v>19.77</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46143</v>
+        <v>45566</v>
       </c>
       <c r="B44" t="n">
-        <v>20.22</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46174</v>
+        <v>45597</v>
       </c>
       <c r="B45" t="n">
-        <v>20.17</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B46" t="n">
+        <v>13.34</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B47" t="n">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B48" t="n">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B49" t="n">
+        <v>16.85</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B50" t="n">
+        <v>23.03</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B51" t="n">
+        <v>17.64</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B52" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B53" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B54" t="n">
+        <v>16.63</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B55" t="n">
+        <v>19.54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B56" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B57" t="n">
+        <v>18.18</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B58" t="n">
+        <v>18.12</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B59" t="n">
+        <v>18.82</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B60" t="n">
+        <v>21.61</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B61" t="n">
+        <v>20.46</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B62" t="n">
+        <v>19.77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B63" t="n">
+        <v>20.22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B64" t="n">
+        <v>20.17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B65" t="n">
         <v>22.55</v>
       </c>
     </row>
@@ -1055,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,6 +1273,11 @@
       <c r="F2" t="n">
         <v>-0.481</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Argentina y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1153,6 +1310,11 @@
       <c r="F3" t="n">
         <v>-0.078</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Argentina y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1185,6 +1347,11 @@
       <c r="F4" t="n">
         <v>-0.048</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Argentina, Trinidad y Tobago y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1217,6 +1384,11 @@
       <c r="F5" t="n">
         <v>-0.001</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Argentina, Guinea Ecuatorial, Trinidad y Tobago y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1249,6 +1421,11 @@
       <c r="F6" t="n">
         <v>-0.06</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1281,6 +1458,11 @@
       <c r="F7" t="n">
         <v>-0.102</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1313,6 +1495,11 @@
       <c r="F8" t="n">
         <v>-0.36</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Guinea Ecuatorial y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1345,6 +1532,11 @@
       <c r="F9" t="n">
         <v>0.48</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Argentina, Guinea Ecuatorial y Estados Unidos</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>text+ocr p16; month stated</t>
@@ -1352,7 +1544,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2021/12/RMensual_v202112.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2021/10/RMensual_v202110.pdf</t>
         </is>
       </c>
     </row>
@@ -1362,23 +1554,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>275.8</v>
+        <v>416.5</v>
       </c>
       <c r="D10" t="n">
-        <v>12.1</v>
+        <v>18.27</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>derived: 2021-11 value / (1 + its monthly change +54.8%)</t>
+          <t>derived: 2022-01 value / (1 + its monthly change -12.6%)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/01/RMensual_v202201.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/03/RMensual_v202203.pdf</t>
         </is>
       </c>
     </row>
@@ -1388,29 +1580,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>427</v>
+        <v>364</v>
       </c>
       <c r="D11" t="n">
-        <v>19.36</v>
+        <v>15.97</v>
       </c>
       <c r="E11" t="n">
-        <v>0.548</v>
+        <v>-0.126</v>
       </c>
       <c r="F11" t="n">
-        <v>0.48</v>
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago y Argentina</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>text+ocr p16; month assumed</t>
+          <t>text+ocr p16; month stated</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/01/RMensual_v202201.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/03/RMensual_v202203.pdf</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1617,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>427</v>
+        <v>422.6</v>
       </c>
       <c r="D12" t="n">
-        <v>18.73</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.48</v>
+        <v>20.53</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>text+ocr p16; month assumed</t>
+          <t>derived: 2023-02 value / (1 + its annual change +5.3%)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/02/RMensual_v202202.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/04/RMensual_v202304.pdf</t>
         </is>
       </c>
     </row>
@@ -1452,29 +1643,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>364</v>
+        <v>429</v>
       </c>
       <c r="D13" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.126</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.6909999999999999</v>
+        <v>18.82</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Trinidad y Tobago, Guinea Ecuatorial y Argentina</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>text+ocr p16; month stated</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/03/RMensual_v202203.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/05/RMensual_v202205.pdf</t>
         </is>
       </c>
     </row>
@@ -1484,23 +1674,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>489.6</v>
+        <v>206</v>
       </c>
       <c r="D14" t="n">
-        <v>21.48</v>
+        <v>9.34</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Guinea Ecuatorial y Argentina</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>derived: 2022-06 value / (1 + its monthly change -13.4%)</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/08/RMensual_v202208.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/06/RMensual_v202206.pdf</t>
         </is>
       </c>
     </row>
@@ -1510,29 +1705,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
       <c r="D15" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.134</v>
+        <v>21.45</v>
       </c>
       <c r="F15" t="n">
-        <v>0.138</v>
+        <v>0.396</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Guinea Ecuatorial, Argentina, Trinidad y Tobago y Estados Unidos, Trinidad y Tobago</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>text+ocr p16; month stated</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/08/RMensual_v202208.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/07/RMensual_v202207.pdf</t>
         </is>
       </c>
     </row>
@@ -1542,20 +1739,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>336</v>
+        <v>424</v>
       </c>
       <c r="D16" t="n">
-        <v>14.74</v>
+        <v>19.22</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.208</v>
+        <v>-0.134</v>
       </c>
       <c r="F16" t="n">
-        <v>0.216</v>
+        <v>0.138</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nigeria, Guinea Ecuatorial, Estados Unidos, Trinidad y Tobago, Argentina y Australia</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1564,7 +1766,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/09/RMensual_v202209.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/08/RMensual_v202208.pdf</t>
         </is>
       </c>
     </row>
@@ -1574,20 +1776,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>556</v>
+        <v>336</v>
       </c>
       <c r="D17" t="n">
-        <v>24.39</v>
+        <v>14.74</v>
       </c>
       <c r="E17" t="n">
-        <v>0.655</v>
+        <v>-0.208</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3</v>
+        <v>0.216</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nigeria, Australia, Guinea Ecuatorial, Argentina y Trinidad y Tobago</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1596,7 +1803,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/10/RMensual_v202210.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/09/RMensual_v202209.pdf</t>
         </is>
       </c>
     </row>
@@ -1606,23 +1813,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>61</v>
+        <v>556</v>
       </c>
       <c r="D18" t="n">
-        <v>2.77</v>
+        <v>24.39</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos, Guinea Ecuatorial y Argentina</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ocr p16; month stated</t>
+          <t>text+ocr p16; month stated</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2022/11/RMensual_v202211.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/10/RMensual_v202210.pdf</t>
         </is>
       </c>
     </row>
@@ -1632,23 +1850,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>400.4</v>
+        <v>469</v>
       </c>
       <c r="D19" t="n">
-        <v>18.15</v>
+        <v>21.26</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Guinea Ecuatorial, Trinidad y Tobago, y Argentina</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>derived: 2023-07 value / (1 + its monthly change -8.6%)</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2023/09/RMensual_v202309.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/11/RMensual_v202211.pdf</t>
         </is>
       </c>
     </row>
@@ -1658,34 +1881,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>366</v>
+        <v>444</v>
       </c>
       <c r="D20" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.08599999999999999</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.089</v>
+        <v>19.48</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Guinea Ecuatorial, Estados Unidos , Argentina y Trinidad y Tobago</t>
+          <t>Guinea Ecuatorial, Estados Unidos, Trinidad y Tobago, y Argentina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>text+ocr p17; month stated</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2023/09/RMensual_v202309.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2022/12/RMensual_v202212.pdf</t>
         </is>
       </c>
     </row>
@@ -1695,23 +1912,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>344.1</v>
+        <v>356</v>
       </c>
       <c r="D21" t="n">
-        <v>15.1</v>
+        <v>16.14</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Guinea Ecuatorial y Argentina</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>derived: 2024-01 value / (1 + its monthly change +1.7%)</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/03/RMensual_v202403.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/01/RMensual_v202301.pdf</t>
         </is>
       </c>
     </row>
@@ -1721,34 +1943,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="D22" t="n">
-        <v>15.35</v>
+        <v>16.89</v>
       </c>
       <c r="E22" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.076</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Guinea Ecuatorial, Trinidad y Tobago y Argentina</t>
+          <t>Trinidad y Tobago, Guinea Ecuatorial y Argentina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>text+ocr p17; month stated</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/03/RMensual_v202403.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/02/RMensual_v202302.pdf</t>
         </is>
       </c>
     </row>
@@ -1758,23 +1980,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="D23" t="n">
-        <v>17.94</v>
+        <v>16.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Guinea Ecuatorial, Trinidad y Tobago y Argentina</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>derived: 2024-04 value / (1 + its monthly change -11.0%)</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/06/RMensual_v202406.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/03/RMensual_v202303.pdf</t>
         </is>
       </c>
     </row>
@@ -1784,34 +2014,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>364</v>
+        <v>445</v>
       </c>
       <c r="D24" t="n">
-        <v>16.5</v>
+        <v>21.61</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.11</v>
+        <v>0.163</v>
       </c>
       <c r="F24" t="n">
-        <v>0.062</v>
+        <v>0.053</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+          <t>Estados Unidos, Trinidad y Tobago y Argentina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>text+ocr p17; month stated</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/06/RMensual_v202406.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/04/RMensual_v202304.pdf</t>
         </is>
       </c>
     </row>
@@ -1821,34 +2051,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="D25" t="n">
-        <v>19.61</v>
+        <v>20.31</v>
       </c>
       <c r="E25" t="n">
-        <v>0.23</v>
+        <v>0.042</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.316</v>
+        <v>0.08</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Estados Unidos, Argentina y Trinidad y Tobago</t>
+          <t>Nigeria, Estados Unidos, Trinidad y Tobago y Argentina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>text+ocr p17; month stated</t>
+          <t>ocr p16; month stated</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/07/RMensual_v202407.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/05/RMensual_v202305.pdf</t>
         </is>
       </c>
     </row>
@@ -1858,34 +2088,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="D26" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.163</v>
+        <v>15.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.064</v>
+        <v>0.666</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+          <t>Guinea Ecuatorial, Trinidad y Tobago, Estados Unidos, y Argentina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>text+ocr p17; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/08/RMensual_v202408.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/06/RMensual_v202306.pdf</t>
         </is>
       </c>
     </row>
@@ -1895,23 +2122,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>475</v>
+        <v>653</v>
       </c>
       <c r="D27" t="n">
-        <v>20.84</v>
+        <v>28.65</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>derived: 2024-08 value / (1 + its monthly change -38.1%)</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/10/RMensual_v202410.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/07/RMensual_v202307.pdf</t>
         </is>
       </c>
     </row>
@@ -1921,34 +2159,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>294</v>
+        <v>400</v>
       </c>
       <c r="D28" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0.381</v>
+        <v>18.13</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.08</v>
+        <v>-0.056</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+          <t>Trinidad y Tobago, Guinea Ecuatorial, Egipto, Estados Unidos y Argentina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>text+ocr p17; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/10/RMensual_v202410.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/08/RMensual_v202308.pdf</t>
         </is>
       </c>
     </row>
@@ -1958,24 +2193,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="D29" t="n">
-        <v>14.37</v>
+        <v>16.06</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.296</v>
+        <v>0.089</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+          <t>Guinea Ecuatorial, Estados Unidos , Argentina y Trinidad y Tobago</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1985,7 +2220,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/11/RMensual_v202411.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/09/RMensual_v202309.pdf</t>
         </is>
       </c>
     </row>
@@ -1995,34 +2230,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>432</v>
+        <v>319</v>
       </c>
       <c r="D30" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.123</v>
+        <v>13.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Argentina y Trinidad y Tobago</t>
+          <t>Trinidad y Tobago, Guinea Ecuatorial, Estados Unidos y Argentina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>text+ocr p17; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2024/12/RMensual_v202412.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/10/RMensual_v202310.pdf</t>
         </is>
       </c>
     </row>
@@ -2032,28 +2261,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.74</v>
+        <v>451</v>
       </c>
       <c r="D31" t="n">
-        <v>0.47</v>
+        <v>20.45</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.038</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Trinidad y Tobago y Argentina</t>
+          <t>Estados Unidos, Trinidad y Tobago, Guinea Ecuatorial, y Argentina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ocr p18; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/04/RMensual_v202504.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/11/RMensual_v202311.pdf</t>
         </is>
       </c>
     </row>
@@ -2063,28 +2298,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.66</v>
+        <v>385</v>
       </c>
       <c r="D32" t="n">
-        <v>0.57</v>
+        <v>16.89</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nigeria, Estados Unidos, Trinidad y Tobago, y Argentina</t>
+          <t>Estados Unidos, Trinidad y Tobago y Argentina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ocr p18; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/06/RMensual_v202506.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2023/12/RMensual_v202312.pdf</t>
         </is>
       </c>
     </row>
@@ -2094,28 +2329,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>39.87</v>
+        <v>359</v>
       </c>
       <c r="D33" t="n">
-        <v>1.81</v>
+        <v>16.27</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.007</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nigeria, Trinidad y Tobago, Estados Unidos y Argentina</t>
+          <t>Guinea Ecuatorial, Trinidad y Tobago y Argentina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ocr p18; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/08/RMensual_v202508.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/01/RMensual_v202401.pdf</t>
         </is>
       </c>
     </row>
@@ -2125,23 +2366,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>496.1</v>
+        <v>344</v>
       </c>
       <c r="D34" t="n">
-        <v>21.76</v>
+        <v>15.09</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.106</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Guinea Ecuatorial, Trinidad y Tobago y Argentina</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>derived: 2025-08 value / (1 + its monthly change -23.6%)</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/10/RMensual_v202510.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/02/RMensual_v202402.pdf</t>
         </is>
       </c>
     </row>
@@ -2151,34 +2403,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="D35" t="n">
-        <v>16.63</v>
+        <v>15.35</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.236</v>
+        <v>0.017</v>
       </c>
       <c r="F35" t="n">
-        <v>0.291</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nigeria, Estados Unidos, Trinidad y Tobago y Argentina</t>
+          <t>Guinea Ecuatorial, Trinidad y Tobago y Argentina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>text p18; month stated</t>
+          <t>text+ocr p17; month stated</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/10/RMensual_v202510.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/03/RMensual_v202403.pdf</t>
         </is>
       </c>
     </row>
@@ -2188,34 +2440,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>431</v>
+        <v>481</v>
       </c>
       <c r="D36" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.135</v>
+        <v>22.56</v>
       </c>
       <c r="F36" t="n">
-        <v>0.357</v>
+        <v>0.081</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Estados Unidos, Nigeria, Trinidad y Tobago y Argentina</t>
+          <t>Estados Unidos, Trinidad y Tobago y Argentina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>text p18; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/11/RMensual_v202511.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/04/RMensual_v202404.pdf</t>
         </is>
       </c>
     </row>
@@ -2225,34 +2474,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="D37" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.296</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-0.298</v>
+        <v>17.9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+          <t>Estados Unidos, Trinidad y Tobago y Argentina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>text p18; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2025/12/RMensual_v202512.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/05/RMensual_v202405.pdf</t>
         </is>
       </c>
     </row>
@@ -2262,34 +2505,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="D38" t="n">
-        <v>18.18</v>
+        <v>16.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.321</v>
+        <v>-0.11</v>
       </c>
       <c r="F38" t="n">
-        <v>0.788</v>
+        <v>0.062</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>text p18; month stated</t>
+          <t>text+ocr p17; month stated</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/01/RMensual_v202601.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/06/RMensual_v202406.pdf</t>
         </is>
       </c>
     </row>
@@ -2299,34 +2542,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="D39" t="n">
-        <v>18.12</v>
+        <v>19.61</v>
       </c>
       <c r="E39" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="F39" t="n">
-        <v>0.36</v>
+        <v>-0.316</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
+          <t>Estados Unidos, Argentina y Trinidad y Tobago</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>text p18; month stated</t>
+          <t>text+ocr p17; month stated</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/02/RMensual_v202602.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/07/RMensual_v202407.pdf</t>
         </is>
       </c>
     </row>
@@ -2336,34 +2579,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>429</v>
+        <v>374</v>
       </c>
       <c r="D40" t="n">
-        <v>18.82</v>
+        <v>16.95</v>
       </c>
       <c r="E40" t="n">
-        <v>0.039</v>
+        <v>-0.163</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.048</v>
+        <v>-0.064</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Trinidad y Tobago, Estados Unidos, y Argentina</t>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>text p18; month stated</t>
+          <t>text+ocr p17; month stated</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/03/RMensual_v202603.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/08/RMensual_v202408.pdf</t>
         </is>
       </c>
     </row>
@@ -2373,34 +2616,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="D41" t="n">
-        <v>21.61</v>
+        <v>20.84</v>
       </c>
       <c r="E41" t="n">
-        <v>0.037</v>
+        <v>0.269</v>
       </c>
       <c r="F41" t="n">
-        <v>0.123</v>
+        <v>0.3</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Australia y Argentina</t>
+          <t>Trinidad y Tobago, Argentina y Estados Unidos</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>text p18; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/04/RMensual_v202604.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/09/RMensual_v202409.pdf</t>
         </is>
       </c>
     </row>
@@ -2410,23 +2653,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>466.3</v>
+        <v>294</v>
       </c>
       <c r="D42" t="n">
-        <v>20.46</v>
+        <v>12.9</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.381</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>derived: 2026-04 value / (1 + its monthly change -6.5%)</t>
+          <t>text+ocr p17; month stated</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/RMensual_v202606.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/10/RMensual_v202410.pdf</t>
         </is>
       </c>
     </row>
@@ -2436,20 +2690,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>436</v>
+        <v>317</v>
       </c>
       <c r="D43" t="n">
-        <v>19.77</v>
+        <v>14.37</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.065</v>
+        <v>0.08</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.142</v>
+        <v>-0.296</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2458,12 +2712,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>text p17; month stated</t>
+          <t>text+ocr p17; month stated</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/RMensual_v202606.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/11/RMensual_v202411.pdf</t>
         </is>
       </c>
     </row>
@@ -2473,29 +2727,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="D44" t="n">
-        <v>20.22</v>
+        <v>18.95</v>
       </c>
       <c r="E44" t="n">
-        <v>0.056</v>
+        <v>0.362</v>
       </c>
       <c r="F44" t="n">
-        <v>0.145</v>
+        <v>0.123</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Argentina y Trinidad y Tobago</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>text p17; month stated</t>
+          <t>text+ocr p17; month stated</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/07/RMensual_v202607.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2024/12/RMensual_v202412.pdf</t>
         </is>
       </c>
     </row>
@@ -2505,29 +2764,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>445</v>
+        <v>224</v>
       </c>
       <c r="D45" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.008999999999999999</v>
+        <v>10.15</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago y Argentina</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>text p17; month stated</t>
+          <t>ocr p17; month stated</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/08/RMensual_v202608.pdf</t>
+          <t>https://www.cne.cl/wp-content/uploads/2025/01/RMensual_v202501.pdf</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2795,696 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>304</v>
+      </c>
+      <c r="D46" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/02/RMensual_v202502.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>451</v>
+      </c>
+      <c r="D47" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ocr p17; month stated</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/03/RMensual_v202503.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>396</v>
+      </c>
+      <c r="D48" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/04/RMensual_v202504.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>384</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/05/RMensual_v202505.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>508</v>
+      </c>
+      <c r="D50" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nigeria, Estados Unidos, Trinidad y Tobago, y Argentina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/06/RMensual_v202506.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>402</v>
+      </c>
+      <c r="D51" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nigeria, Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/07/RMensual_v202507.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>441</v>
+      </c>
+      <c r="D52" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nigeria, Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/08/RMensual_v202508.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>497</v>
+      </c>
+      <c r="D53" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ocr p18; month stated</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/09/RMensual_v202509.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>379</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.236</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nigeria, Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/10/RMensual_v202510.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>431</v>
+      </c>
+      <c r="D55" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Nigeria, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/11/RMensual_v202511.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>303</v>
+      </c>
+      <c r="D56" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.298</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2025/12/RMensual_v202512.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>401</v>
+      </c>
+      <c r="D57" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/01/RMensual_v202601.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>413</v>
+      </c>
+      <c r="D58" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Australia, Estados Unidos, Trinidad y Tobago y Argentina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/02/RMensual_v202602.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>429</v>
+      </c>
+      <c r="D59" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos, y Argentina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/03/RMensual_v202603.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>445</v>
+      </c>
+      <c r="D60" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Australia y Argentina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>text p18; month stated</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/04/RMensual_v202604.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>466.3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>derived: 2026-04 value / (1 + its monthly change -6.5%)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/06/RMensual_v202606.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>436</v>
+      </c>
+      <c r="D62" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.142</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>text p17; month stated</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/06/RMensual_v202606.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>461</v>
+      </c>
+      <c r="D63" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>text p17; month stated</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/07/RMensual_v202607.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>445</v>
+      </c>
+      <c r="D64" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>text p17; month stated</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/08/RMensual_v202608.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C65" t="n">
         <v>514</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D65" t="n">
         <v>22.55</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E65" t="n">
         <v>0.155</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F65" t="n">
         <v>0.035</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Trinidad y Tobago, Estados Unidos y Argentina</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>text p17; month stated</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>https://www.cne.cl/wp-content/uploads/2026/09/RMensual_v202609.pdf</t>
         </is>

--- a/output/Data and Chart Outputs/chile_gas_imports.xlsx
+++ b/output/Data and Chart Outputs/chile_gas_imports.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -635,20 +635,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Months with no value: 2021-09, 2021-10, 2021-11. CNE published no table for them (its Nov 2021-Feb 2022 reports repeat the Aug 2021 table), and the annual changes in the Sep-Nov 2022 tables needed to derive them do not OCR cleanly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Origins lists the source countries the report names for that month's gas imports.</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Comision Nacional de Energia (CNE), Reporte Mensual del Sector Energetico, section 'Importaciones y Exportaciones de Combustibles' (Aduana data via COMEX). The Report column holds the PDF used.</t>
         </is>

--- a/output/Data and Chart Outputs/chile_gas_imports.xlsx
+++ b/output/Data and Chart Outputs/chile_gas_imports.xlsx
@@ -21,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmm/yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,11 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -385,7 +385,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -423,6 +423,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -542,7 +548,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -580,6 +586,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -981,6 +993,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -1016,6 +1029,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -1030,6 +1044,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -1051,6 +1066,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
@@ -1146,7 +1162,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1169,7 +1185,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1192,7 +1208,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1215,7 +1231,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1238,7 +1254,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1261,7 +1277,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1284,7 +1300,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1307,7 +1323,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1330,7 +1346,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1353,7 +1369,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1376,7 +1392,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1399,7 +1415,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1422,7 +1438,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1445,7 +1461,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1468,7 +1484,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1491,7 +1507,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1514,7 +1530,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1537,7 +1553,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1560,7 +1576,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1583,7 +1599,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1606,7 +1622,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1629,7 +1645,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1652,7 +1668,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1675,7 +1691,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1698,7 +1714,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1721,7 +1737,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1744,7 +1760,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1783,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1790,7 +1806,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1813,7 +1829,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1836,7 +1852,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1859,7 +1875,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1882,7 +1898,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1905,7 +1921,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1928,7 +1944,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1951,7 +1967,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1974,7 +1990,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1997,7 +2013,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2020,7 +2036,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2043,7 +2059,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2066,7 +2082,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2089,7 +2105,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2112,7 +2128,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2135,7 +2151,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2158,7 +2174,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2181,7 +2197,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2204,7 +2220,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2227,7 +2243,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2250,7 +2266,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2273,7 +2289,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2296,7 +2312,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2319,7 +2335,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2342,7 +2358,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2365,7 +2381,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2388,7 +2404,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2411,7 +2427,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2434,7 +2450,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2457,7 +2473,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2480,7 +2496,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2503,7 +2519,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2526,7 +2542,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2549,7 +2565,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2572,7 +2588,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2595,7 +2611,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2618,7 +2634,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="H66" t="n">
@@ -2626,7 +2642,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="H67" t="n">
@@ -2634,7 +2650,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="H68" t="n">
@@ -2677,7 +2693,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2688,7 +2704,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -2699,7 +2715,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -2710,7 +2726,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -2721,7 +2737,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -2732,7 +2748,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -2743,7 +2759,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -2754,7 +2770,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -2765,7 +2781,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -2776,7 +2792,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -2787,7 +2803,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -2798,7 +2814,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2809,7 +2825,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2820,7 +2836,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2831,7 +2847,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2842,7 +2858,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2853,7 +2869,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2864,7 +2880,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2875,7 +2891,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2886,7 +2902,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2897,7 +2913,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2908,7 +2924,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2919,7 +2935,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2930,7 +2946,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2941,7 +2957,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2952,7 +2968,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2963,7 +2979,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2974,7 +2990,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2985,7 +3001,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2996,7 +3012,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -3007,7 +3023,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -3018,7 +3034,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -3029,7 +3045,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3040,7 +3056,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -3051,7 +3067,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -3062,7 +3078,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -3073,7 +3089,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -3084,7 +3100,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -3095,7 +3111,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -3106,7 +3122,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -3117,7 +3133,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -3128,7 +3144,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">

--- a/output/Data and Chart Outputs/chile_gas_imports.xlsx
+++ b/output/Data and Chart Outputs/chile_gas_imports.xlsx
@@ -155,7 +155,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile natural gas imports by use and entry region (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Chile natural gas imports by use and entry region (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -185,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$68</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -213,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$68</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -241,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$68</f>
+              <f>'Chart'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -269,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$68</f>
+              <f>'Chart'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -297,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$68</f>
+              <f>'Chart'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -325,40 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$68</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$H$2:$H$68</f>
+              <f>'Chart'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -458,6 +431,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Chile domestic gas production (Magallanes) (to Jun/24)</a:t>
             </a:r>
           </a:p>
@@ -613,7 +587,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1004,7 +978,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monthly from January 2021: import workbook to 2026-04, then the monthly report (to 2026-07). 61 months are in both sources; mean absolute difference 0.1% (both are the same customs data; the report rounds to whole kt and its 2021-2025 values are read by OCR).</t>
+          <t>Monthly from January 2021: import workbook to 2026-08, then the monthly report (to 2026-08). 64 months are in both sources; mean absolute difference 0.1% (both are the same customs data; the report rounds to whole kt and its 2021-2025 values are read by OCR).</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1036,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>This is a split of imports, not of demand: it shows imported gas for petrochemical use, but Methanex also uses domestic Magallanes gas, which is not in it. Coverage: 2021-01 to 2026-04; the workbook is re-read when CNE uploads a new one.</t>
+          <t>This is a split of imports, not of demand: it shows imported gas for petrochemical use, but Methanex also uses domestic Magallanes gas, which is not in it. Coverage: 2021-01 to 2026-08; the workbook is re-read when CNE uploads a new one.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1155,11 +1129,6 @@
           <t>Argentina pipeline - Magallanes (methanol)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Total, monthly report (no split)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -2637,24 +2606,92 @@
       <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="H66" t="n">
-        <v>20.22</v>
+      <c r="B66" t="n">
+        <v>6.143</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8.802</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.065</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
         <v>46174</v>
       </c>
-      <c r="H67" t="n">
-        <v>20.17</v>
+      <c r="B67" t="n">
+        <v>3.978</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10.854</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.137</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="H68" t="n">
-        <v>22.55</v>
+      <c r="B68" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="D68" t="n">
+        <v>9.336</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2.381</v>
+      </c>
+      <c r="D69" t="n">
+        <v>6.167</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.665</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6304,18 +6341,24 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>461</v>
+        <v>460.8</v>
       </c>
       <c r="D66" t="n">
-        <v>20.22</v>
+        <v>19.89</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CNE Reporte Mensual</t>
-        </is>
+          <t>CNE import workbook (customs)</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>460.8</v>
       </c>
       <c r="G66" t="n">
         <v>461</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.0004</v>
       </c>
       <c r="I66" t="n">
         <v>0.056</v>
@@ -6347,15 +6390,21 @@
         <v>445</v>
       </c>
       <c r="D67" t="n">
-        <v>20.17</v>
+        <v>19.79</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CNE Reporte Mensual</t>
-        </is>
+          <t>CNE import workbook (customs)</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>445</v>
       </c>
       <c r="G67" t="n">
         <v>445</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>-0.034</v>
@@ -6384,19 +6433,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>514</v>
+        <v>514.2</v>
       </c>
       <c r="D68" t="n">
-        <v>22.55</v>
+        <v>22.23</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CNE Reporte Mensual</t>
-        </is>
+          <t>CNE import workbook (customs)</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>514.2</v>
       </c>
       <c r="G68" t="n">
         <v>514</v>
       </c>
+      <c r="H68" t="n">
+        <v>0.0004</v>
+      </c>
       <c r="I68" t="n">
         <v>0.155</v>
       </c>
@@ -6417,6 +6472,30 @@
         <is>
           <t>https://www.cne.cl/wp-content/uploads/2026/09/RMensual_v202609.pdf</t>
         </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>318.9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CNE import workbook (customs)</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>318.9</v>
       </c>
     </row>
   </sheetData>
@@ -6430,7 +6509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6560,7 +6639,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6693,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6747,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6801,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6855,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6909,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6963,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6938,7 +7017,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -6992,7 +7071,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7125,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7233,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7287,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7341,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7395,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7449,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7503,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7557,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7611,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7665,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7719,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7773,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7827,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7881,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7935,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7989,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -7964,7 +8043,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8097,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8151,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8205,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8259,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8313,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8367,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8421,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8475,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8529,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8583,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8637,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8691,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8745,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8799,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8853,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8907,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8961,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8936,7 +9015,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -8990,7 +9069,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9123,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9177,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9231,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9285,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9339,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9393,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9447,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9501,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9555,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9609,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9663,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9717,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9771,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9825,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9879,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9933,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9987,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
@@ -9962,7 +10041,223 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.cne.cl/wp-content/uploads/2026/06/importaciones-web.xlsx</t>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8.802</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="H66" t="n">
+        <v>6.143</v>
+      </c>
+      <c r="I66" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="J66" t="n">
+        <v>14.00555555555556</v>
+      </c>
+      <c r="K66" t="n">
+        <v>272.8705970124339</v>
+      </c>
+      <c r="L66" t="n">
+        <v>35.86242547883599</v>
+      </c>
+      <c r="M66" t="n">
+        <v>33.01309523809524</v>
+      </c>
+      <c r="N66" t="n">
+        <v>51806.88172</v>
+      </c>
+      <c r="O66" t="n">
+        <v>140033.01868</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10.854</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.978</v>
+      </c>
+      <c r="I67" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="J67" t="n">
+        <v>10.00396825396825</v>
+      </c>
+      <c r="K67" t="n">
+        <v>325.6213985838624</v>
+      </c>
+      <c r="L67" t="n">
+        <v>35.09706187883599</v>
+      </c>
+      <c r="M67" t="n">
+        <v>34.11353174603175</v>
+      </c>
+      <c r="N67" t="n">
+        <v>51167.58248</v>
+      </c>
+      <c r="O67" t="n">
+        <v>87758.09638999999</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>9.336</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="H68" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="I68" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>289.4050927403439</v>
+      </c>
+      <c r="L68" t="n">
+        <v>34.26001084748678</v>
+      </c>
+      <c r="M68" t="n">
+        <v>34.11353174603175</v>
+      </c>
+      <c r="N68" t="n">
+        <v>81051.88071000001</v>
+      </c>
+      <c r="O68" t="n">
+        <v>162635.64507</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="D69" t="n">
+        <v>6.167</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.381</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="I69" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.150456349206349</v>
+      </c>
+      <c r="K69" t="n">
+        <v>191.1847878969577</v>
+      </c>
+      <c r="L69" t="n">
+        <v>32.71117547619048</v>
+      </c>
+      <c r="M69" t="n">
+        <v>51.62047619047619</v>
+      </c>
+      <c r="N69" t="n">
+        <v>54280.58028</v>
+      </c>
+      <c r="O69" t="n">
+        <v>55433.96629</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>https://www.cne.cl/wp-content/uploads/2026/10/importaciones-web.xlsx</t>
         </is>
       </c>
     </row>
